--- a/ksta_管理シート_20260617.xlsx
+++ b/ksta_管理シート_20260617.xlsx
@@ -1676,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1965,6 +1965,9 @@
           <t>⑧ お問い合わせフォーム実装（Formspree: xqeojrpr）LP内に埋め込み</t>
         </is>
       </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="14" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -1972,6 +1975,9 @@
           <t>⑨ setup.html作成：クライアント向けお店情報入力フォーム（インスタURL・サイトURL）</t>
         </is>
       </c>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="14" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1979,11 +1985,149 @@
           <t>⑩ sales_kit Section09追加：返信メール・納品メールテンプレート</t>
         </is>
       </c>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="14" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>⑪ sites_list.csv・CLAUDE.md・メモリ更新</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Section10追加：追いメッセージ3パターン（友人・面識あり・コールドDM）</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>制作アンケート季節セレクター修正（春夏秋冬→1〜12月）</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ハッシュタグ処理改善（#付き/なし両対応・1行1タグ・フォールバック）</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>既存ジェネ更新ボタンAPIキーIDバグ修正</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LP価格表示を税込¥4,980・¥9,800に修正</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Section11追加：専用ジェネ体験後→LP営業DM2パターン</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>

--- a/ksta_管理シート_20260617.xlsx
+++ b/ksta_管理シート_20260617.xlsx
@@ -1676,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2128,6 +2128,72 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>友人3店反応確認：ターゲットズレ判明（インスタ特化なし・専属担当あり）</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ターゲット再定義：投稿停止中の個人オーナー小規模飲食店に絞る</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>コールドDM方針確定：京都市内からリスト作成→DM開始予定</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>対応中</t>
         </is>
       </c>
     </row>
